--- a/examples/multitrait_multimethod/target.xlsx
+++ b/examples/multitrait_multimethod/target.xlsx
@@ -13,9 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Attention Problems</t>
   </si>
   <si>
     <t xml:space="preserve">Externalizing</t>
@@ -597,1089 +600,1254 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>0.0994959655436646</v>
+        <v>0.0657217116217292</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>0.0432851706006051</v>
+        <v>-0.0531231175700351</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>0.440941320009021</v>
+        <v>-0.0154658308399976</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>-0.0643873916882304</v>
+        <v>-0.446933678589383</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.0172338125127647</v>
+        <v>0.0522468758909481</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>0.00306899188457164</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0.175694190833058</v>
+        <v>0.146262852560327</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.0653755541448634</v>
+        <v>-0.0234439489559932</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.458113178418214</v>
+        <v>-0.0394391654808463</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>-0.0168731829735583</v>
+        <v>-0.466059954454332</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.00668941608369269</v>
+        <v>0.000936841582444394</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0.0134204654708302</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0.389095648828472</v>
+        <v>0.358846802426267</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0.0350187221821257</v>
+        <v>0.0553414694893262</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.563505343706062</v>
+        <v>0.011046454007811</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>-0.00596648752871048</v>
+        <v>-0.58399986728123</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>-0.0182379510737668</v>
+        <v>-0.0400935910500296</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0.0118225747479388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.355136048679864</v>
+        <v>0.332297348609625</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>-0.0163102784854094</v>
+        <v>0.0320272459303061</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.482435237605181</v>
+        <v>0.00455698778840763</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.0191791948461224</v>
+        <v>-0.496890396353022</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.0280782216924283</v>
+        <v>-0.0507420236734523</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>-0.0392301057363848</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.166802692664214</v>
+        <v>0.109024701587445</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>-0.00590259792415791</v>
+        <v>-0.118495007745814</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.558512621703971</v>
+        <v>-0.00184183491321792</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.00625164100167361</v>
+        <v>-0.565517717194162</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.0243714446843707</v>
+        <v>-0.0175976273703492</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>-0.0467865076831395</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.356338950240279</v>
+        <v>0.329487372010397</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.0440000381896899</v>
+        <v>0.0684483920400709</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.607013052362262</v>
+        <v>-0.00702285060677515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-0.0161351136695499</v>
+        <v>-0.626225555656329</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>-0.0570355392864784</v>
+        <v>-0.0264020766574023</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>-0.0188707526869958</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.0742493337740158</v>
+        <v>0.000477680455358253</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>-0.0265152024954365</v>
+        <v>-0.137992061816215</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.287799433083533</v>
+        <v>0.0972752130521517</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.0248471541162764</v>
+        <v>-0.29988956828429</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.0814110112961289</v>
+        <v>-0.0500884873380451</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.0230452937576072</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.0860433938894827</v>
+        <v>0.00646590756042861</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>-0.0187610459533727</v>
+        <v>-0.150765244706244</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.365200869013203</v>
+        <v>0.056200585503954</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>0.100745840611874</v>
+        <v>-0.375328042875002</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.0393007627882452</v>
+        <v>-0.118540872421604</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>-0.026601421915432</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.175326039283197</v>
+        <v>0.0933824286885883</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>-0.0312192023841863</v>
+        <v>-0.244676176034074</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.321461491789067</v>
+        <v>0.0596992400881429</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>0.0461906884642803</v>
+        <v>-0.326761464838829</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.2215736683555</v>
+        <v>-0.0571692755207245</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0.0925977041675258</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.027877593421273</v>
+        <v>-0.0208087423511341</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>-0.00435554318889304</v>
+        <v>-0.124427145251422</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.457748707688352</v>
+        <v>-0.0320983786981923</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.0268014753466887</v>
+        <v>-0.45729979862933</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>-0.0216809924704469</v>
+        <v>-0.0203494422997132</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>-0.0936063703983066</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.063021459763523</v>
+        <v>-0.0239591589567523</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0.00351160704158862</v>
+        <v>-0.244183680016567</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.499388416978637</v>
+        <v>-0.0141785915584508</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.0936476233294353</v>
+        <v>-0.500271178900631</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.090606243396811</v>
+        <v>-0.0881912502275344</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>-0.0270717440177316</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.0436170068302718</v>
+        <v>-0.0319010060765902</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>0.022060086425361</v>
+        <v>-0.172168513838409</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.364340374373555</v>
+        <v>0.0513215041787945</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-0.00958461795769661</v>
+        <v>-0.37249054768891</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.115680993836653</v>
+        <v>-0.00623255471827505</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0.0567774618780572</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>-0.00287087308337655</v>
+        <v>0.0179701370602029</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>0.257515482943497</v>
+        <v>0.00971087589699636</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.51258069070427</v>
+        <v>-0.310693290032421</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>-0.0128123168655734</v>
+        <v>-0.503968198889863</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>-0.0694611889670163</v>
+        <v>0.0536404941084053</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.00502956671765263</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.0423269546922508</v>
+        <v>0.0581720764851744</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>0.202050851787999</v>
+        <v>0.0315903064737764</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.482631000083664</v>
+        <v>-0.215322479711446</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.068950004950776</v>
+        <v>-0.47945790531896</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.0528653151606698</v>
+        <v>0.0883674719375208</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0.0176256399230608</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>-0.0240923042049149</v>
+        <v>-0.00381230389068225</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>0.24642650470977</v>
+        <v>0.0611184966259956</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.522210259597754</v>
+        <v>-0.257764130621202</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-0.0557977904747511</v>
+        <v>-0.517555615545825</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>-0.118624313777507</v>
+        <v>0.0803303754212426</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>-0.0126980151304913</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.00303757366630426</v>
+        <v>0.00123939759434467</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.202105743093913</v>
+        <v>-0.051538584775092</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.462609513311601</v>
+        <v>-0.216355635139739</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.0385065367379613</v>
+        <v>-0.455428770094421</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.00950144567079334</v>
+        <v>0.0666193453256283</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.0436455396354388</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>-0.00994389010134222</v>
+        <v>-0.0398079378009234</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>0.22081817693609</v>
+        <v>-0.126641526308205</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.454838999839873</v>
+        <v>-0.216038405317417</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>0.0617936518871596</v>
+        <v>-0.446511336111826</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.0534201783164573</v>
+        <v>-0.032390659314225</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.0712494214136847</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>-0.0157797778450906</v>
+        <v>0.0147251292736453</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.289381255260245</v>
+        <v>0.0240782420140629</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.568333922934767</v>
+        <v>-0.362056943591773</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>-0.0270869624855542</v>
+        <v>-0.559602197057771</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>-0.0920575687110969</v>
+        <v>0.0772978763878211</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>-0.00575279775299846</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.32172806548306</v>
+        <v>0.291498323513929</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>0.0378992989526546</v>
+        <v>0.0353441125835868</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.00107930434442717</v>
+        <v>-0.011867759348751</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.350825220084733</v>
+        <v>-0.0150177208577266</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>-0.010013560898428</v>
+        <v>-0.379319381523086</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>0.0379986417170098</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.432160865449</v>
+        <v>0.396186908173764</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0.000741422498635192</v>
+        <v>0.0429420435856189</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.0213348575514702</v>
+        <v>-0.0199171017604913</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0.483370240689327</v>
+        <v>-0.0374848440309272</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>-0.0527225176227369</v>
+        <v>-0.513214868068279</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>-0.0216928332435324</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.617719907411377</v>
+        <v>0.584850393891782</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>0.0201200593121327</v>
+        <v>0.138337937379925</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.0282619828660472</v>
+        <v>0.0419423883302041</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0.46581055074706</v>
+        <v>-0.0583005330844413</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>-0.0301389826034453</v>
+        <v>-0.534207879187536</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>0.0647895521266987</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.516451709321024</v>
+        <v>0.459045983381076</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>-0.0459372040553788</v>
+        <v>-0.0127775871064469</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>-0.00423387344670303</v>
+        <v>0.0609888148979566</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.475106175126989</v>
+        <v>-0.0167600900506601</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.0505207447826947</v>
+        <v>-0.521615488580025</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>0.0421487065325891</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.357696198505953</v>
+        <v>0.266402246585608</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>-0.0757375508314371</v>
+        <v>-0.157333998180681</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.0189239812162706</v>
+        <v>0.0404826084005719</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>0.576965386779029</v>
+        <v>-0.0304487125299681</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.048314810101859</v>
+        <v>-0.597026207381449</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>-0.0381602324347041</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.593337501734292</v>
+        <v>0.56279296186861</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>0.0171091049208087</v>
+        <v>0.128774732488274</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.03401718789535</v>
+        <v>0.00987490564415595</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>0.498624105270393</v>
+        <v>-0.0604458868218215</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>-0.0575281945098446</v>
+        <v>-0.555592107020454</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>0.0264229609111598</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0.0836588681341791</v>
+        <v>-0.0241627229628055</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>-0.00387163901434381</v>
+        <v>-0.191817482208105</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.0188560229599618</v>
+        <v>0.0627901193974066</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.436009588599834</v>
+        <v>-0.0276882685539166</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.0524404556259142</v>
+        <v>-0.457517925405455</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>0.00516399722557576</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.186706355479892</v>
+        <v>0.0734070050731309</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>-0.107057159386982</v>
+        <v>-0.241166386346729</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>-0.0037192042180151</v>
+        <v>0.0539792868385054</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.605559636351645</v>
+        <v>-0.00156321251864851</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.0261851043444903</v>
+        <v>-0.611857908105849</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>-0.104942078317034</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.258956084395164</v>
+        <v>0.146739034731269</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>-0.148937127020626</v>
+        <v>-0.418959125439134</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.02792435823797</v>
+        <v>0.0757710542860541</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>0.348937719289272</v>
+        <v>-0.0244726192284439</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.345452973610873</v>
+        <v>-0.336133593825737</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>0.0813160876088277</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0.0441199505388211</v>
+        <v>-0.0354677031145076</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>0.072563374533258</v>
+        <v>-0.19226425971172</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>-0.0509668483991177</v>
+        <v>-0.121013837609783</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.627096003071929</v>
+        <v>0.0560655888300019</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>-0.0123117359097151</v>
+        <v>-0.601246733086764</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>-0.0473788500628746</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0.074119588080115</v>
+        <v>-0.0345560711844252</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>0.0279807792740624</v>
+        <v>-0.216248027294228</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>-0.022225765620883</v>
+        <v>-0.0275177594489324</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.619833687371093</v>
+        <v>0.0201982084458955</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.00951876396523476</v>
+        <v>-0.619257533553497</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>-0.040193363251591</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0.0557995192476921</v>
+        <v>-0.0312767050624766</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>0.00227175181985876</v>
+        <v>-0.209108790485721</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>-0.0446061297248035</v>
+        <v>0.0308787347866631</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>0.361901123002858</v>
+        <v>0.0421773350845658</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.112080828555183</v>
+        <v>-0.365508116114514</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>0.0462436359717663</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>-0.0181653475715272</v>
+        <v>0.0313357126443701</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>0.36152830033523</v>
+        <v>0.0452028418256031</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>-0.00445922516421452</v>
+        <v>-0.536232946198275</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>0.469176969809293</v>
+        <v>0.0389623322319077</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>-0.132839928520869</v>
+        <v>-0.397017523893413</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>0.00346500686992334</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>-0.0195075613169593</v>
+        <v>0.0165551784413737</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>0.227582481492673</v>
+        <v>0.008500501312865</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.0430772456967718</v>
+        <v>-0.358795696032777</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>0.282868774849783</v>
+        <v>-0.0207690763981998</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>-0.0821730335456686</v>
+        <v>-0.223167013298175</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>-0.0146364805186374</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>-0.009231336684303</v>
+        <v>0.0017345130695761</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>0.288988975123474</v>
+        <v>0.00285598280142368</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>-0.0137537048790121</v>
+        <v>-0.361105788238707</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>0.453776924059778</v>
+        <v>0.0313637201663533</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>-0.0930853056971838</v>
+        <v>-0.403958860096736</v>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>0.022721866973174</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.0291779045447354</v>
+        <v>0.0187971285753046</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>0.274161776498511</v>
+        <v>-0.0827498064338655</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0.0108956237951148</v>
+        <v>-0.332939908641599</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>0.460614840062238</v>
+        <v>0.00569843053678305</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0.00376897863260251</v>
+        <v>-0.410318530242944</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>0.0738813956533594</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>-0.0420819512019936</v>
+        <v>-0.064308836190114</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>0.271038782989936</v>
+        <v>-0.114865400138386</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.00811172290979941</v>
+        <v>-0.334272443955635</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>0.502872095553755</v>
+        <v>0.0103631637135314</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>-0.0191925703731802</v>
+        <v>-0.446164362691666</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>0.0404366933757896</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>-0.0470316230429648</v>
+        <v>0.0137240074150885</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>0.353514019718624</v>
+        <v>0.0318574679699375</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>-0.00308048404912329</v>
+        <v>-0.591172147408622</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.447881947488525</v>
+        <v>0.0467129347478559</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>-0.136490615859322</v>
+        <v>-0.363280023090283</v>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>-0.0256641647516399</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>0.433960967254697</v>
+        <v>0.431656829802764</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>0.110220423793972</v>
+        <v>-0.0601656695451585</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.000381352716030787</v>
+        <v>-0.0193464210560481</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>-0.0428890007984136</v>
+        <v>-0.0085063340678696</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.377305029390515</v>
+        <v>0.0177054355675918</v>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>0.380477800136203</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>0.544480516187684</v>
+        <v>0.552612403223812</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>0.130520103853348</v>
+        <v>-0.0427584671384855</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>-0.00840306511483252</v>
+        <v>-0.056533680728423</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.0030998489679765</v>
+        <v>0.000195473587954554</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.404603575277233</v>
+        <v>-0.0277474020793733</v>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>0.415413946443416</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>0.724776197126667</v>
+        <v>0.755460135873783</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>0.0530181015424491</v>
+        <v>0.0180813182921684</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>-0.0435948338014525</v>
+        <v>-0.0193853846701969</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>-0.00142057801895603</v>
+        <v>0.0311344224292496</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.406559220604015</v>
+        <v>-0.0341026625522477</v>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>0.398300930419982</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>0.581972211565692</v>
+        <v>0.598162892384324</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>-0.0778259518844288</v>
+        <v>-0.129834760688644</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>-0.0258579012329269</v>
+        <v>0.00135246741362315</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>-0.0196107620160414</v>
+        <v>0.0257965430663313</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.417859704997786</v>
+        <v>0.0173650229707997</v>
+      </c>
+      <c r="G41" s="1" t="n">
+        <v>0.267968739166673</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>0.49631307725336</v>
+        <v>0.467708041823201</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>-0.0678437225288705</v>
+        <v>-0.344753210940448</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>0.00000829353365119498</v>
+        <v>-0.0177546095277324</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.0171537745751368</v>
+        <v>0.00962166284118009</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.583269255011295</v>
+        <v>0.00392958179643831</v>
+      </c>
+      <c r="G42" s="1" t="n">
+        <v>0.337380431135287</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>0.727593644866453</v>
+        <v>0.764326915666042</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>0.0308475174418734</v>
+        <v>0.0246861946994845</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>-0.0304134118098227</v>
+        <v>-0.0198840437285924</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>-0.0096206683719241</v>
+        <v>0.0190583525051273</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.387352508254815</v>
+        <v>-0.0228848320269794</v>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>0.367466623737662</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>0.19140045332959</v>
+        <v>0.108080400708862</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>-0.105530745206406</v>
+        <v>-0.635184332611005</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.0489541066227193</v>
+        <v>-0.0339411780165713</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.00825147668922954</v>
+        <v>-0.0209592090740814</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.699868494738536</v>
+        <v>0.0600805896010743</v>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>0.301075307958165</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>0.169778292891362</v>
+        <v>0.0990869565316916</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>-0.030372439986673</v>
+        <v>-0.465524117571142</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.00676481658611804</v>
+        <v>-0.0158532766625735</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.0309412689188142</v>
+        <v>0.00994506335746142</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.560566757613337</v>
+        <v>0.00729758901599414</v>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>0.298692170412168</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>0.254752442181807</v>
+        <v>0.170638517561663</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>-0.119275623066234</v>
+        <v>-0.638010979203172</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.00125038870316208</v>
+        <v>-0.0170330085793037</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.0312376179058877</v>
+        <v>0.0252988834422591</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.735714573054694</v>
+        <v>0.0317092392778233</v>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>0.329790907090557</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>0.117161084309808</v>
+        <v>0.016537375584248</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>0.0475251080964576</v>
+        <v>-0.631825604442974</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.0613051301479124</v>
+        <v>-0.0688743381580756</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.0323357581601013</v>
+        <v>-0.0366981519361899</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.735193867379269</v>
+        <v>0.0248390054895549</v>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>0.427580149978616</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>0.0481240410593579</v>
+        <v>-0.0665042447021885</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>-0.0280367275172219</v>
+        <v>-0.696946965598409</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.0425890314874934</v>
+        <v>-0.0177890717311104</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.0159299452363185</v>
+        <v>-0.0156083522069694</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.747127640483115</v>
+        <v>0.0469025293537669</v>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>0.377095670145597</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>0.0675560505259449</v>
+        <v>-0.0380750173269464</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>-0.0973253665694944</v>
+        <v>-0.59538335183835</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.00371038305766073</v>
+        <v>0.0318228159230486</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.0727934388264832</v>
+        <v>0.0168992805351418</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.598795341023534</v>
+        <v>-0.0239242210835283</v>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>0.253845245300977</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>0.014408485443107</v>
+        <v>0.001429963865168</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>0.674827071213101</v>
+        <v>0.150225990705229</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>-0.038456251765631</v>
+        <v>-0.180092344653911</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>-0.0383979322066062</v>
+        <v>0.0211048457677084</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>0.265805431133306</v>
+        <v>-0.0200769304818813</v>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>0.711413911370482</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>0.00757658787645456</v>
+        <v>-0.00944745906396621</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>0.452766776113771</v>
+        <v>0.0702852403136901</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>-0.0424530383058964</v>
+        <v>-0.114517996062772</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>0.00114587074696133</v>
+        <v>0.0305280713920756</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>0.202822152505339</v>
+        <v>-0.0399903068451146</v>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>0.488072101086544</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>0.0470468412545624</v>
+        <v>0.0264053459741329</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>0.541755521966664</v>
+        <v>0.161905328334871</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.0207522404079012</v>
+        <v>-0.0773569204313223</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>-0.0810353807553403</v>
+        <v>-0.0441342217478586</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>0.207290219604687</v>
+        <v>0.0102592432610108</v>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>0.601413252060192</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>0.0663626966428699</v>
+        <v>0.0116385978542037</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>0.513802297969363</v>
+        <v>-0.0764202676491798</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.0186307385218861</v>
+        <v>-0.0914294369078537</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>-0.0670510676775789</v>
+        <v>-0.0313752724659817</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0.446203157861579</v>
+        <v>0.0225925907269578</v>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>0.699242802750691</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>-0.00368257602321266</v>
+        <v>-0.0806243617602367</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>0.431433021720099</v>
+        <v>-0.242207387714565</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.0322344378645512</v>
+        <v>-0.120795438543278</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>0.0298438012586735</v>
+        <v>-0.0328095276448835</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0.484206812478342</v>
+        <v>-0.0403009178950076</v>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>0.60376788725924</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>0.004578279567737</v>
+        <v>-0.022999203403336</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>0.656015718631135</v>
+        <v>0.127173052463235</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>-0.0329777346589744</v>
+        <v>-0.147239062174295</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>-0.0324861819147137</v>
+        <v>0.0146889231342986</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.27743214537459</v>
+        <v>-0.0306504761559952</v>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>0.71496556224138</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:F55">
+  <conditionalFormatting sqref="B2:G55">
     <cfRule type="expression" dxfId="0" priority="4">
       <formula>B2&lt;=-0.5</formula>
     </cfRule>
@@ -1722,6 +1890,9 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -1731,16 +1902,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>0.250754029190348</v>
+        <v>-0.469590903419078</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>0.0000000000000000416333634234434</v>
+        <v>-0.0793047550244572</v>
       </c>
       <c r="E2" s="1" t="n">
+        <v>0.0000000000000000277555756156289</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>-0.0000000000000000555111512312578</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>0.0000000000000000555111512312578</v>
       </c>
     </row>
     <row r="3">
@@ -1748,19 +1922,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0.250754029190348</v>
+        <v>-0.469590903419078</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.0000000000000000277555756156289</v>
+        <v>0.034858733598651</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>-0.0000000000000000416333634234434</v>
+        <v>0.0000000000000000555111512312578</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>-0.0000000000000000416333634234434</v>
+        <v>-0.0000000000000000555111512312578</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0.0000000000000000555111512312578</v>
       </c>
     </row>
     <row r="4">
@@ -1768,19 +1945,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0.0000000000000000416333634234434</v>
+        <v>-0.0793047550244572</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0.0000000000000000277555756156289</v>
+        <v>0.034858733598651</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.297691439591031</v>
+        <v>0.0000000000000000138777878078145</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.239820475872646</v>
+        <v>-0.0000000000000000138777878078145</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>-0.0000000000000000277555756156289</v>
       </c>
     </row>
     <row r="5">
@@ -1788,19 +1968,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.0000000000000000555111512312578</v>
+        <v>0.0000000000000000277555756156289</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>-0.0000000000000000416333634234434</v>
+        <v>0.0000000000000000555111512312578</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.297691439591031</v>
+        <v>0.0000000000000000138777878078145</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.301544225596608</v>
+        <v>0.294540584697348</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>-0.27557269069471</v>
       </c>
     </row>
     <row r="6">
@@ -1808,23 +1991,49 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0000000000000000555111512312578</v>
+        <v>0</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>-0.0000000000000000416333634234434</v>
+        <v>-0.0000000000000000555111512312578</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.239820475872646</v>
+        <v>-0.0000000000000000138777878078145</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.301544225596608</v>
+        <v>0.294540584697348</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="G6" s="1" t="n">
+        <v>-0.277981094976856</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>-0.0000000000000000555111512312578</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.0000000000000000555111512312578</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>-0.0000000000000000277555756156289</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>-0.27557269069471</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>-0.277981094976856</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:F6">
+  <conditionalFormatting sqref="B2:G7">
     <cfRule type="expression" dxfId="0" priority="4">
       <formula>B2&lt;=-0.5</formula>
     </cfRule>

--- a/examples/multitrait_multimethod/target.xlsx
+++ b/examples/multitrait_multimethod/target.xlsx
@@ -13,12 +13,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Attention Problems</t>
   </si>
   <si>
     <t xml:space="preserve">Externalizing</t>
@@ -600,1265 +597,1156 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>0.0657217116217292</v>
+        <v>-0.0994960389812513</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>-0.0531231175700351</v>
+        <v>0.043285821432689</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>-0.0154658308399976</v>
+        <v>0.440941296525429</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>-0.446933678589383</v>
+        <v>-0.0643874680792878</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.0522468758909481</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>0.00306899188457164</v>
+        <v>0.0172337649851566</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0.146262852560327</v>
+        <v>-0.175694080324873</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>-0.0234439489559932</v>
+        <v>0.0653762260946941</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>-0.0394391654808463</v>
+        <v>0.458113045256177</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>-0.466059954454332</v>
+        <v>-0.0168730644431689</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.000936841582444394</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.0134204654708302</v>
+        <v>0.00668960131560902</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0.358846802426267</v>
+        <v>-0.389095535618356</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0.0553414694893262</v>
+        <v>0.0350196331313173</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.011046454007811</v>
+        <v>0.563505262961788</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>-0.58399986728123</v>
+        <v>-0.00596645927957912</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>-0.0400935910500296</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.0118225747479388</v>
+        <v>-0.0182377714701389</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.332297348609625</v>
+        <v>-0.35513489215276</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.0320272459303061</v>
+        <v>-0.0163094401847481</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.00455698778840763</v>
+        <v>0.482434634905124</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-0.496890396353022</v>
+        <v>0.0191798749858954</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.0507420236734523</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>-0.0392301057363848</v>
+        <v>-0.0280774473376623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.109024701587445</v>
+        <v>-0.166803528851012</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>-0.118495007745814</v>
+        <v>-0.0059019740916438</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>-0.00184183491321792</v>
+        <v>0.558512947275156</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>-0.565517717194162</v>
+        <v>0.00625138050389139</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-0.0175976273703492</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>-0.0467865076831395</v>
+        <v>0.0243708576839954</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.329487372010397</v>
+        <v>-0.356338995835724</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.0684483920400709</v>
+        <v>0.044001046425344</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>-0.00702285060677515</v>
+        <v>0.607013051658258</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-0.626225555656329</v>
+        <v>-0.0161351003792411</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>-0.0264020766574023</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>-0.0188707526869958</v>
+        <v>-0.0570353875238137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.000477680455358253</v>
+        <v>-0.0742487625748488</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>-0.137992061816215</v>
+        <v>-0.0265154789999724</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.0972752130521517</v>
+        <v>0.287800102356005</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.29988956828429</v>
+        <v>0.0248475197978004</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-0.0500884873380451</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.0230452937576072</v>
+        <v>0.081411431593121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.00646590756042861</v>
+        <v>-0.0860438705889181</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>-0.150765244706244</v>
+        <v>-0.0187608467309411</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.056200585503954</v>
+        <v>0.365201033163086</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>-0.375328042875002</v>
+        <v>0.100745864163855</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>-0.118540872421604</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>-0.026601421915432</v>
+        <v>0.0393002346896923</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.0933824286885883</v>
+        <v>-0.175326267822604</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>-0.244676176034074</v>
+        <v>-0.0312188497259928</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.0596992400881429</v>
+        <v>0.321461189317648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>-0.326761464838829</v>
+        <v>0.0461910084632867</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>-0.0571692755207245</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>0.0925977041675258</v>
+        <v>0.221573427518775</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>-0.0208087423511341</v>
+        <v>-0.027877460371956</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>-0.124427145251422</v>
+        <v>-0.00435500543116896</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>-0.0320983786981923</v>
+        <v>0.457748289336181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-0.45729979862933</v>
+        <v>0.0268018811602401</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>-0.0203494422997132</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>-0.0936063703983066</v>
+        <v>-0.0216809092297206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.0239591589567523</v>
+        <v>-0.0630219694333207</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>-0.244183680016567</v>
+        <v>0.00351216896376079</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>-0.0141785915584508</v>
+        <v>0.499387723942926</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>-0.500271178900631</v>
+        <v>0.0936479270826516</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.0881912502275344</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>-0.0270717440177316</v>
+        <v>0.0906058989843895</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.0319010060765902</v>
+        <v>-0.0436171495257116</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>-0.172168513838409</v>
+        <v>0.0220603847125113</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.0513215041787945</v>
+        <v>0.36434025961197</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-0.37249054768891</v>
+        <v>-0.00958446749433371</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>-0.00623255471827505</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>0.0567774618780572</v>
+        <v>0.115680949275006</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.0179701370602029</v>
+        <v>0.00287092585502087</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>0.00971087589699636</v>
+        <v>0.257516249855087</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>-0.310693290032421</v>
+        <v>0.512581125582187</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>-0.503968198889863</v>
+        <v>-0.0128124886224526</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.0536404941084053</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>0.00502956671765263</v>
+        <v>-0.0694609096313291</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.0581720764851744</v>
+        <v>-0.0423273744155478</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>0.0315903064737764</v>
+        <v>0.202051632943556</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>-0.215322479711446</v>
+        <v>0.482630909266713</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.47945790531896</v>
+        <v>-0.0689503204724035</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.0883674719375208</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>0.0176256399230608</v>
+        <v>-0.0528652247958685</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>-0.00381230389068225</v>
+        <v>0.0240920866927551</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>0.0611184966259956</v>
+        <v>0.246427500084087</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>-0.257764130621202</v>
+        <v>0.522210654816676</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-0.517555615545825</v>
+        <v>-0.0557982036488879</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.0803303754212426</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>-0.0126980151304913</v>
+        <v>-0.118624167776159</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0.00123939759434467</v>
+        <v>-0.00303747068699593</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>-0.051538584775092</v>
+        <v>0.20210657481227</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>-0.216355635139739</v>
+        <v>0.462609791980676</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.455428770094421</v>
+        <v>-0.0385067422756728</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.0666193453256283</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>0.0436455396354388</v>
+        <v>0.00950152641816126</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>-0.0398079378009234</v>
+        <v>0.00994372290419773</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>-0.126641526308205</v>
+        <v>0.220818341594516</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>-0.216038405317417</v>
+        <v>0.454838463486119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>-0.446511336111826</v>
+        <v>0.0617936924237904</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>-0.032390659314225</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>0.0712494214136847</v>
+        <v>0.053420383513188</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.0147251292736453</v>
+        <v>0.0157795420439332</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.0240782420140629</v>
+        <v>0.289382296205629</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-0.362056943591773</v>
+        <v>0.56833447318748</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>-0.559602197057771</v>
+        <v>-0.0270873538849986</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.0772978763878211</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>-0.00575279775299846</v>
+        <v>-0.0920573791943294</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0.291498323513929</v>
+        <v>-0.321727856976657</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>0.0353441125835868</v>
+        <v>0.0378990166679925</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>-0.011867759348751</v>
+        <v>0.00107923897758101</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>-0.0150177208577266</v>
+        <v>0.350825426683083</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>-0.379319381523086</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>0.0379986417170098</v>
+        <v>-0.0100137380146065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0.396186908173764</v>
+        <v>-0.43216123248928</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0.0429420435856189</v>
+        <v>0.000740918755003627</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>-0.0199171017604913</v>
+        <v>0.0213345729477702</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.0374848440309272</v>
+        <v>0.483371237550306</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>-0.513214868068279</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>-0.0216928332435324</v>
+        <v>-0.0527231805217617</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0.584850393891782</v>
+        <v>-0.617719611433877</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>0.138337937379925</v>
+        <v>0.0201198707449137</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.0419423883302041</v>
+        <v>0.0282618939160115</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.0583005330844413</v>
+        <v>0.465810537232558</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>-0.534207879187536</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>0.0647895521266987</v>
+        <v>-0.0301390427351185</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0.459045983381076</v>
+        <v>-0.516451418974088</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>-0.0127775871064469</v>
+        <v>-0.0459377069511307</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.0609888148979566</v>
+        <v>-0.00423403348001238</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>-0.0167600900506601</v>
+        <v>0.475106572359331</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>-0.521615488580025</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>0.0421487065325891</v>
+        <v>0.0505204825270348</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0.266402246585608</v>
+        <v>-0.357695325255973</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>-0.157333998180681</v>
+        <v>-0.0757386100554015</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.0404826084005719</v>
+        <v>0.018923630620494</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>-0.0304487125299681</v>
+        <v>0.576966811715027</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>-0.597026207381449</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>-0.0381602324347041</v>
+        <v>0.0483144229193796</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0.56279296186861</v>
+        <v>-0.593336320943205</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>0.128774732488274</v>
+        <v>0.0171088801987668</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.00987490564415595</v>
+        <v>0.03401726783229</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>-0.0604458868218215</v>
+        <v>0.498623842812822</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>-0.555592107020454</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>0.0264229609111598</v>
+        <v>-0.0575278259886567</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>-0.0241627229628055</v>
+        <v>-0.0836576909650068</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>-0.191817482208105</v>
+        <v>-0.00387241559253401</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.0627901193974066</v>
+        <v>0.0188560013839654</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>-0.0276882685539166</v>
+        <v>0.436010570009308</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>-0.457517925405455</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>0.00516399722557576</v>
+        <v>0.0524405132415527</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0.0734070050731309</v>
+        <v>-0.186705594863874</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>-0.241166386346729</v>
+        <v>-0.107057989339109</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.0539792868385054</v>
+        <v>-0.00371935879873821</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>-0.00156321251864851</v>
+        <v>0.605560610611583</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>-0.611857908105849</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>-0.104942078317034</v>
+        <v>0.0261847929926318</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0.146739034731269</v>
+        <v>-0.258955509478126</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>-0.418959125439134</v>
+        <v>-0.148938229124515</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.0757710542860541</v>
+        <v>0.027924074799171</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-0.0244726192284439</v>
+        <v>0.348939084337016</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>-0.336133593825737</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>0.0813160876088277</v>
+        <v>0.345452971427003</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>-0.0354677031145076</v>
+        <v>-0.0441186445830075</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>-0.19226425971172</v>
+        <v>0.072562345101008</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>-0.121013837609783</v>
+        <v>-0.0509668336449155</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.0560655888300019</v>
+        <v>0.627096749178508</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>-0.601246733086764</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>-0.0473788500628746</v>
+        <v>-0.0123118302247651</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>-0.0345560711844252</v>
+        <v>-0.0741184674075873</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>-0.216248027294228</v>
+        <v>0.0279798230021841</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>-0.0275177594489324</v>
+        <v>-0.0222258166405959</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.0201982084458955</v>
+        <v>0.619834927500786</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>-0.619257533553497</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>-0.040193363251591</v>
+        <v>0.00951853894064712</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>-0.0312767050624766</v>
+        <v>-0.0557985084926926</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>-0.209108790485721</v>
+        <v>0.00227107247193968</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>0.0308787347866631</v>
+        <v>-0.044606099790655</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>0.0421773350845658</v>
+        <v>0.36190192917021</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>-0.365508116114514</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>0.0462436359717663</v>
+        <v>0.112080937921277</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.0313357126443701</v>
+        <v>0.0181652632293075</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>0.0452028418256031</v>
+        <v>0.361527477405394</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>-0.536232946198275</v>
+        <v>-0.00445869262938254</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>0.0389623322319077</v>
+        <v>0.469176141443949</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>-0.397017523893413</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>0.00346500686992334</v>
+        <v>-0.132839806196678</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.0165551784413737</v>
+        <v>0.0195068873103161</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>0.008500501312865</v>
+        <v>0.227581903884382</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>-0.358795696032777</v>
+        <v>0.0430774159152277</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>-0.0207690763981998</v>
+        <v>0.282867742301973</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>-0.223167013298175</v>
-      </c>
-      <c r="G33" s="1" t="n">
-        <v>-0.0146364805186374</v>
+        <v>-0.0821731842229775</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.0017345130695761</v>
+        <v>0.00923103272791889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>0.00285598280142368</v>
+        <v>0.288987784680533</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>-0.361105788238707</v>
+        <v>-0.0137530532115684</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>0.0313637201663533</v>
+        <v>0.453775765268019</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>-0.403958860096736</v>
-      </c>
-      <c r="G34" s="1" t="n">
-        <v>0.022721866973174</v>
+        <v>-0.0930850274787932</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.0187971285753046</v>
+        <v>-0.0291768158837246</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>-0.0827498064338655</v>
+        <v>0.274162132723454</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>-0.332939908641599</v>
+        <v>0.0108954466258702</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>0.00569843053678305</v>
+        <v>0.460615836234356</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.410318530242944</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>0.0738813956533594</v>
+        <v>0.00376865890246183</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>-0.064308836190114</v>
+        <v>0.0420821871266927</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>-0.114865400138386</v>
+        <v>0.271037817361864</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>-0.334272443955635</v>
+        <v>0.00811206487096836</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>0.0103631637135314</v>
+        <v>0.502871446211095</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>-0.446164362691666</v>
-      </c>
-      <c r="G36" s="1" t="n">
-        <v>0.0404366933757896</v>
+        <v>-0.0191925423842733</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>0.0137240074150885</v>
+        <v>0.0470310804905215</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>0.0318574679699375</v>
+        <v>0.353513190039341</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>-0.591172147408622</v>
+        <v>-0.00307992080996349</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.0467129347478559</v>
+        <v>0.44788095755238</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>-0.363280023090283</v>
-      </c>
-      <c r="G37" s="1" t="n">
-        <v>-0.0256641647516399</v>
+        <v>-0.136490614572768</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>0.431656829802764</v>
+        <v>-0.433960086186576</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>-0.0601656695451585</v>
+        <v>0.110220326612683</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>-0.0193464210560481</v>
+        <v>0.000381575950249398</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>-0.0085063340678696</v>
+        <v>-0.0428885930566046</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.0177054355675918</v>
-      </c>
-      <c r="G38" s="1" t="n">
-        <v>0.380477800136203</v>
+        <v>0.377304818189699</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>0.552612403223812</v>
+        <v>-0.544481731220918</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>-0.0427584671384855</v>
+        <v>0.130520536313269</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>-0.056533680728423</v>
+        <v>-0.00840322481551343</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.000195473587954554</v>
+        <v>0.00309929119260329</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>-0.0277474020793733</v>
-      </c>
-      <c r="G39" s="1" t="n">
-        <v>0.415413946443416</v>
+        <v>0.404603957152376</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>0.755460135873783</v>
+        <v>-0.724773718698109</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>0.0180813182921684</v>
+        <v>0.0530183331242574</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>-0.0193853846701969</v>
+        <v>-0.0435942741698646</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.0311344224292496</v>
+        <v>-0.00141970373189379</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>-0.0341026625522477</v>
-      </c>
-      <c r="G40" s="1" t="n">
-        <v>0.398300930419982</v>
+        <v>0.406559268231212</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>0.598162892384324</v>
+        <v>-0.581972658185908</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>-0.129834760688644</v>
+        <v>-0.0778259590116456</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.00135246741362315</v>
+        <v>-0.0258581220683837</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.0257965430663313</v>
+        <v>-0.0196107091781679</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.0173650229707997</v>
-      </c>
-      <c r="G41" s="1" t="n">
-        <v>0.267968739166673</v>
+        <v>0.417859586436111</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>0.467708041823201</v>
+        <v>-0.496313871287413</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>-0.344753210940448</v>
+        <v>-0.0678437503579091</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>-0.0177546095277324</v>
+        <v>0.00000806654834519369</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.00962166284118009</v>
+        <v>0.0171538504195737</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.00392958179643831</v>
-      </c>
-      <c r="G42" s="1" t="n">
-        <v>0.337380431135287</v>
+        <v>0.58326854878611</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>0.764326915666042</v>
+        <v>-0.727595496188921</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>0.0246861946994845</v>
+        <v>0.0308477152811923</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>-0.0198840437285924</v>
+        <v>-0.0304137916066296</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.0190583525051273</v>
+        <v>-0.00962136461657814</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>-0.0228848320269794</v>
-      </c>
-      <c r="G43" s="1" t="n">
-        <v>0.367466623737662</v>
+        <v>0.387352650673429</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>0.108080400708862</v>
+        <v>-0.191401618594468</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>-0.635184332611005</v>
+        <v>-0.105530284811867</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>-0.0339411780165713</v>
+        <v>0.0489538411221657</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>-0.0209592090740814</v>
+        <v>0.00825211755732236</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.0600805896010743</v>
-      </c>
-      <c r="G44" s="1" t="n">
-        <v>0.301075307958165</v>
+        <v>0.699865830713311</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>0.0990869565316916</v>
+        <v>-0.169778084339281</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>-0.465524117571142</v>
+        <v>-0.0303730090930621</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>-0.0158532766625735</v>
+        <v>0.00676480693504647</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.00994506335746142</v>
+        <v>0.0309417449975747</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.00729758901599414</v>
-      </c>
-      <c r="G45" s="1" t="n">
-        <v>0.298692170412168</v>
+        <v>0.560567343942986</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>0.170638517561663</v>
+        <v>-0.254753355285644</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>-0.638010979203172</v>
+        <v>-0.119274858418072</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>-0.0170330085793037</v>
+        <v>0.00125036591182872</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.0252988834422591</v>
+        <v>0.0312383880649815</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.0317092392778233</v>
-      </c>
-      <c r="G46" s="1" t="n">
-        <v>0.329790907090557</v>
+        <v>0.735711439794544</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>0.016537375584248</v>
+        <v>-0.117162209484301</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>-0.631825604442974</v>
+        <v>0.047524960465648</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>-0.0688743381580756</v>
+        <v>0.0613051241010793</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>-0.0366981519361899</v>
+        <v>0.0323361854471167</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.0248390054895549</v>
-      </c>
-      <c r="G47" s="1" t="n">
-        <v>0.427580149978616</v>
+        <v>0.735191974949799</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>-0.0665042447021885</v>
+        <v>-0.0481256711616164</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>-0.696946965598409</v>
+        <v>-0.0280368367668672</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>-0.0177890717311104</v>
+        <v>0.0425888941457078</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>-0.0156083522069694</v>
+        <v>0.0159303150462347</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.0469025293537669</v>
-      </c>
-      <c r="G48" s="1" t="n">
-        <v>0.377095670145597</v>
+        <v>0.747125036170389</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>-0.0380750173269464</v>
+        <v>-0.0675559880724038</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>-0.59538335183835</v>
+        <v>-0.0973260995678208</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.0318228159230486</v>
+        <v>0.00371033727390243</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.0168992805351418</v>
+        <v>0.0727941839878385</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>-0.0239242210835283</v>
-      </c>
-      <c r="G49" s="1" t="n">
-        <v>0.253845245300977</v>
+        <v>0.598795479040359</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>0.001429963865168</v>
+        <v>-0.0144081389326515</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>0.150225990705229</v>
+        <v>0.674829387207591</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>-0.180092344653911</v>
+        <v>-0.0384559108227052</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>0.0211048457677084</v>
+        <v>-0.0383994255259256</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>-0.0200769304818813</v>
-      </c>
-      <c r="G50" s="1" t="n">
-        <v>0.711413911370482</v>
+        <v>0.26580654012363</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>-0.00944745906396621</v>
+        <v>-0.00757646371516078</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>0.0702852403136901</v>
+        <v>0.452767322977336</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>-0.114517996062772</v>
+        <v>-0.0424526631839724</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>0.0305280713920756</v>
+        <v>0.00114505485054386</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>-0.0399903068451146</v>
-      </c>
-      <c r="G51" s="1" t="n">
-        <v>0.488072101086544</v>
+        <v>0.202822736643838</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>0.0264053459741329</v>
+        <v>-0.0470465837573028</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>0.161905328334871</v>
+        <v>0.541756193160326</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>-0.0773569204313223</v>
+        <v>0.0207528719412255</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>-0.0441342217478586</v>
+        <v>-0.0810362444753856</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>0.0102592432610108</v>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>0.601413252060192</v>
+        <v>0.207291228291027</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>0.0116385978542037</v>
+        <v>-0.0663628167341162</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>-0.0764202676491798</v>
+        <v>0.513803065772297</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>-0.0914294369078537</v>
+        <v>0.0186311695572389</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>-0.0313752724659817</v>
+        <v>-0.0670520380049386</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0.0225925907269578</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>0.699242802750691</v>
+        <v>0.446203886104744</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>-0.0806243617602367</v>
+        <v>0.0036830471097905</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>-0.242207387714565</v>
+        <v>0.431433855358602</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>-0.120795438543278</v>
+        <v>0.0322346779932143</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.0328095276448835</v>
+        <v>0.029843245321604</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.0403009178950076</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>0.60376788725924</v>
+        <v>0.484207678891175</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>-0.022999203403336</v>
+        <v>-0.00457837798356689</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>0.127173052463235</v>
+        <v>0.656015690463905</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>-0.147239062174295</v>
+        <v>-0.0329768966733411</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>0.0146889231342986</v>
+        <v>-0.0324872224951402</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>-0.0306504761559952</v>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>0.71496556224138</v>
+        <v>0.277432865692094</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:G55">
+  <conditionalFormatting sqref="B2:B55">
+    <cfRule type="expression" dxfId="0" priority="20">
+      <formula>IFERROR(AND(ISNUMBER(B2),B2&lt;=-0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="19">
+      <formula>IFERROR(AND(ISNUMBER(B2),B2&gt;-0.50000000000000000,B2&lt;=-0.20000000000000001),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="18">
+      <formula>IFERROR(AND(ISNUMBER(B2),B2&gt;0.20000000000000001,B2&lt;=0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="17">
+      <formula>IFERROR(AND(ISNUMBER(B2),B2&gt;0.50000000000000000),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C55">
+    <cfRule type="expression" dxfId="0" priority="16">
+      <formula>IFERROR(AND(ISNUMBER(C2),C2&lt;=-0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="15">
+      <formula>IFERROR(AND(ISNUMBER(C2),C2&gt;-0.50000000000000000,C2&lt;=-0.20000000000000001),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="14">
+      <formula>IFERROR(AND(ISNUMBER(C2),C2&gt;0.20000000000000001,C2&lt;=0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="13">
+      <formula>IFERROR(AND(ISNUMBER(C2),C2&gt;0.50000000000000000),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D55">
+    <cfRule type="expression" dxfId="0" priority="12">
+      <formula>IFERROR(AND(ISNUMBER(D2),D2&lt;=-0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="11">
+      <formula>IFERROR(AND(ISNUMBER(D2),D2&gt;-0.50000000000000000,D2&lt;=-0.20000000000000001),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="10">
+      <formula>IFERROR(AND(ISNUMBER(D2),D2&gt;0.20000000000000001,D2&lt;=0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="9">
+      <formula>IFERROR(AND(ISNUMBER(D2),D2&gt;0.50000000000000000),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E55">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>IFERROR(AND(ISNUMBER(E2),E2&lt;=-0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="7">
+      <formula>IFERROR(AND(ISNUMBER(E2),E2&gt;-0.50000000000000000,E2&lt;=-0.20000000000000001),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>IFERROR(AND(ISNUMBER(E2),E2&gt;0.20000000000000001,E2&lt;=0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="5">
+      <formula>IFERROR(AND(ISNUMBER(E2),E2&gt;0.50000000000000000),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F55">
     <cfRule type="expression" dxfId="0" priority="4">
-      <formula>B2&lt;=-0.5</formula>
+      <formula>IFERROR(AND(ISNUMBER(F2),F2&lt;=-0.50000000000000000),FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="3">
-      <formula>AND(B2&gt;-0.5,B2&lt;-0.2)</formula>
+      <formula>IFERROR(AND(ISNUMBER(F2),F2&gt;-0.50000000000000000,F2&lt;=-0.20000000000000001),FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="2">
-      <formula>AND(B2&gt;0.2,B2&lt;0.5)</formula>
+      <formula>IFERROR(AND(ISNUMBER(F2),F2&gt;0.20000000000000001,F2&lt;=0.50000000000000000),FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="1">
-      <formula>B2&gt;=0.5</formula>
+      <formula>IFERROR(AND(ISNUMBER(F2),F2&gt;0.50000000000000000),FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1890,9 +1778,6 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -1902,19 +1787,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>-0.469590903419078</v>
+        <v>-0.250752966301378</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>-0.0793047550244572</v>
+        <v>0.0000000000000000208166817117217</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.0000000000000000277555756156289</v>
+        <v>0.0000000000000000208166817117217</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>-0.0000000000000000555111512312578</v>
+        <v>-0.0000000000000000416333634234434</v>
       </c>
     </row>
     <row r="3">
@@ -1922,22 +1804,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>-0.469590903419078</v>
+        <v>-0.250752966301378</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.034858733598651</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.0000000000000000555111512312578</v>
+        <v>-0.0000000000000000138777878078145</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>-0.0000000000000000555111512312578</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.0000000000000000555111512312578</v>
+        <v>-0.0000000000000000138777878078145</v>
       </c>
     </row>
     <row r="4">
@@ -1945,22 +1824,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>-0.0793047550244572</v>
+        <v>0.0000000000000000208166817117217</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0.034858733598651</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.0000000000000000138777878078145</v>
+        <v>0.2976912992148</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>-0.0000000000000000138777878078145</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>-0.0000000000000000277555756156289</v>
+        <v>0.23981962772674</v>
       </c>
     </row>
     <row r="5">
@@ -1968,22 +1844,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0000000000000000277555756156289</v>
+        <v>0.0000000000000000208166817117217</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.0000000000000000555111512312578</v>
+        <v>-0.0000000000000000138777878078145</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.0000000000000000138777878078145</v>
+        <v>0.2976912992148</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.294540584697348</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>-0.27557269069471</v>
+        <v>0.301546020439029</v>
       </c>
     </row>
     <row r="6">
@@ -1991,60 +1864,90 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0</v>
+        <v>-0.0000000000000000416333634234434</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>-0.0000000000000000555111512312578</v>
+        <v>-0.0000000000000000138777878078145</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>-0.0000000000000000138777878078145</v>
+        <v>0.23981962772674</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.294540584697348</v>
+        <v>0.301546020439029</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>-0.277981094976856</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>-0.0000000000000000555111512312578</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>0.0000000000000000555111512312578</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>-0.0000000000000000277555756156289</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>-0.27557269069471</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>-0.277981094976856</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:G7">
+  <conditionalFormatting sqref="B2:B6">
+    <cfRule type="expression" dxfId="0" priority="20">
+      <formula>IFERROR(AND(ISNUMBER(B2),B2&lt;=-0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="19">
+      <formula>IFERROR(AND(ISNUMBER(B2),B2&gt;-0.50000000000000000,B2&lt;=-0.20000000000000001),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="18">
+      <formula>IFERROR(AND(ISNUMBER(B2),B2&gt;0.20000000000000001,B2&lt;=0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="17">
+      <formula>IFERROR(AND(ISNUMBER(B2),B2&gt;0.50000000000000000),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C6">
+    <cfRule type="expression" dxfId="0" priority="16">
+      <formula>IFERROR(AND(ISNUMBER(C2),C2&lt;=-0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="15">
+      <formula>IFERROR(AND(ISNUMBER(C2),C2&gt;-0.50000000000000000,C2&lt;=-0.20000000000000001),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="14">
+      <formula>IFERROR(AND(ISNUMBER(C2),C2&gt;0.20000000000000001,C2&lt;=0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="13">
+      <formula>IFERROR(AND(ISNUMBER(C2),C2&gt;0.50000000000000000),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D6">
+    <cfRule type="expression" dxfId="0" priority="12">
+      <formula>IFERROR(AND(ISNUMBER(D2),D2&lt;=-0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="11">
+      <formula>IFERROR(AND(ISNUMBER(D2),D2&gt;-0.50000000000000000,D2&lt;=-0.20000000000000001),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="10">
+      <formula>IFERROR(AND(ISNUMBER(D2),D2&gt;0.20000000000000001,D2&lt;=0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="9">
+      <formula>IFERROR(AND(ISNUMBER(D2),D2&gt;0.50000000000000000),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E6">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>IFERROR(AND(ISNUMBER(E2),E2&lt;=-0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="7">
+      <formula>IFERROR(AND(ISNUMBER(E2),E2&gt;-0.50000000000000000,E2&lt;=-0.20000000000000001),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>IFERROR(AND(ISNUMBER(E2),E2&gt;0.20000000000000001,E2&lt;=0.50000000000000000),FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="5">
+      <formula>IFERROR(AND(ISNUMBER(E2),E2&gt;0.50000000000000000),FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="expression" dxfId="0" priority="4">
-      <formula>B2&lt;=-0.5</formula>
+      <formula>IFERROR(AND(ISNUMBER(F2),F2&lt;=-0.50000000000000000),FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="3">
-      <formula>AND(B2&gt;-0.5,B2&lt;-0.2)</formula>
+      <formula>IFERROR(AND(ISNUMBER(F2),F2&gt;-0.50000000000000000,F2&lt;=-0.20000000000000001),FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="2">
-      <formula>AND(B2&gt;0.2,B2&lt;0.5)</formula>
+      <formula>IFERROR(AND(ISNUMBER(F2),F2&gt;0.20000000000000001,F2&lt;=0.50000000000000000),FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="1">
-      <formula>B2&gt;=0.5</formula>
+      <formula>IFERROR(AND(ISNUMBER(F2),F2&gt;0.50000000000000000),FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/examples/multitrait_multimethod/target.xlsx
+++ b/examples/multitrait_multimethod/target.xlsx
@@ -603,7 +603,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>-0.0994960389812513</v>
+        <v>0.0994960389812513</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>0.043285821432689</v>
@@ -623,7 +623,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>-0.175694080324873</v>
+        <v>0.175694080324873</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0.0653762260946941</v>
@@ -643,7 +643,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>-0.389095535618356</v>
+        <v>0.389095535618356</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>0.0350196331313173</v>
@@ -663,7 +663,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.35513489215276</v>
+        <v>0.35513489215276</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>-0.0163094401847481</v>
@@ -683,7 +683,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>-0.166803528851012</v>
+        <v>0.166803528851012</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>-0.0059019740916438</v>
@@ -703,7 +703,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>-0.356338995835724</v>
+        <v>0.356338995835724</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0.044001046425344</v>
@@ -723,7 +723,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>-0.0742487625748488</v>
+        <v>0.0742487625748488</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>-0.0265154789999724</v>
@@ -743,7 +743,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>-0.0860438705889181</v>
+        <v>0.0860438705889181</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>-0.0187608467309411</v>
@@ -763,7 +763,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>-0.175326267822604</v>
+        <v>0.175326267822604</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>-0.0312188497259928</v>
@@ -783,7 +783,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>-0.027877460371956</v>
+        <v>0.027877460371956</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>-0.00435500543116896</v>
@@ -803,7 +803,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.0630219694333207</v>
+        <v>0.0630219694333207</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>0.00351216896376079</v>
@@ -823,7 +823,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.0436171495257116</v>
+        <v>0.0436171495257116</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0.0220603847125113</v>
@@ -843,7 +843,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0.00287092585502087</v>
+        <v>-0.00287092585502087</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>0.257516249855087</v>
@@ -863,7 +863,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>-0.0423273744155478</v>
+        <v>0.0423273744155478</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>0.202051632943556</v>
@@ -883,7 +883,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.0240920866927551</v>
+        <v>-0.0240920866927551</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>0.246427500084087</v>
@@ -903,7 +903,7 @@
         <v>21</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>-0.00303747068699593</v>
+        <v>0.00303747068699593</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>0.20210657481227</v>
@@ -923,7 +923,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0.00994372290419773</v>
+        <v>-0.00994372290419773</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>0.220818341594516</v>
@@ -943,7 +943,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0.0157795420439332</v>
+        <v>-0.0157795420439332</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>0.289382296205629</v>
@@ -963,7 +963,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>-0.321727856976657</v>
+        <v>0.321727856976657</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>0.0378990166679925</v>
@@ -983,7 +983,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>-0.43216123248928</v>
+        <v>0.43216123248928</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>0.000740918755003627</v>
@@ -1003,7 +1003,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>-0.617719611433877</v>
+        <v>0.617719611433877</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>0.0201198707449137</v>
@@ -1023,7 +1023,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>-0.516451418974088</v>
+        <v>0.516451418974088</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>-0.0459377069511307</v>
@@ -1043,7 +1043,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>-0.357695325255973</v>
+        <v>0.357695325255973</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>-0.0757386100554015</v>
@@ -1063,7 +1063,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>-0.593336320943205</v>
+        <v>0.593336320943205</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>0.0171088801987668</v>
@@ -1083,7 +1083,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>-0.0836576909650068</v>
+        <v>0.0836576909650068</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>-0.00387241559253401</v>
@@ -1103,7 +1103,7 @@
         <v>31</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>-0.186705594863874</v>
+        <v>0.186705594863874</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>-0.107057989339109</v>
@@ -1123,7 +1123,7 @@
         <v>32</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>-0.258955509478126</v>
+        <v>0.258955509478126</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>-0.148938229124515</v>
@@ -1143,7 +1143,7 @@
         <v>33</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>-0.0441186445830075</v>
+        <v>0.0441186445830075</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>0.072562345101008</v>
@@ -1163,7 +1163,7 @@
         <v>34</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>-0.0741184674075873</v>
+        <v>0.0741184674075873</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>0.0279798230021841</v>
@@ -1183,7 +1183,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>-0.0557985084926926</v>
+        <v>0.0557985084926926</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>0.00227107247193968</v>
@@ -1203,7 +1203,7 @@
         <v>36</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0.0181652632293075</v>
+        <v>-0.0181652632293075</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>0.361527477405394</v>
@@ -1223,7 +1223,7 @@
         <v>37</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0.0195068873103161</v>
+        <v>-0.0195068873103161</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>0.227581903884382</v>
@@ -1243,7 +1243,7 @@
         <v>38</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0.00923103272791889</v>
+        <v>-0.00923103272791889</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>0.288987784680533</v>
@@ -1263,7 +1263,7 @@
         <v>39</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>-0.0291768158837246</v>
+        <v>0.0291768158837246</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>0.274162132723454</v>
@@ -1283,7 +1283,7 @@
         <v>40</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>0.0420821871266927</v>
+        <v>-0.0420821871266927</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>0.271037817361864</v>
@@ -1303,7 +1303,7 @@
         <v>41</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>0.0470310804905215</v>
+        <v>-0.0470310804905215</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>0.353513190039341</v>
@@ -1323,7 +1323,7 @@
         <v>42</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>-0.433960086186576</v>
+        <v>0.433960086186576</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>0.110220326612683</v>
@@ -1343,7 +1343,7 @@
         <v>43</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>-0.544481731220918</v>
+        <v>0.544481731220918</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>0.130520536313269</v>
@@ -1363,7 +1363,7 @@
         <v>44</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>-0.724773718698109</v>
+        <v>0.724773718698109</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>0.0530183331242574</v>
@@ -1383,7 +1383,7 @@
         <v>45</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>-0.581972658185908</v>
+        <v>0.581972658185908</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>-0.0778259590116456</v>
@@ -1403,7 +1403,7 @@
         <v>46</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>-0.496313871287413</v>
+        <v>0.496313871287413</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>-0.0678437503579091</v>
@@ -1423,7 +1423,7 @@
         <v>47</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>-0.727595496188921</v>
+        <v>0.727595496188921</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>0.0308477152811923</v>
@@ -1443,7 +1443,7 @@
         <v>48</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>-0.191401618594468</v>
+        <v>0.191401618594468</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>-0.105530284811867</v>
@@ -1463,7 +1463,7 @@
         <v>49</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>-0.169778084339281</v>
+        <v>0.169778084339281</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>-0.0303730090930621</v>
@@ -1483,7 +1483,7 @@
         <v>50</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>-0.254753355285644</v>
+        <v>0.254753355285644</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>-0.119274858418072</v>
@@ -1503,7 +1503,7 @@
         <v>51</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>-0.117162209484301</v>
+        <v>0.117162209484301</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>0.047524960465648</v>
@@ -1523,7 +1523,7 @@
         <v>52</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>-0.0481256711616164</v>
+        <v>0.0481256711616164</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>-0.0280368367668672</v>
@@ -1543,7 +1543,7 @@
         <v>53</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>-0.0675559880724038</v>
+        <v>0.0675559880724038</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>-0.0973260995678208</v>
@@ -1563,7 +1563,7 @@
         <v>54</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>-0.0144081389326515</v>
+        <v>0.0144081389326515</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>0.674829387207591</v>
@@ -1583,7 +1583,7 @@
         <v>55</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>-0.00757646371516078</v>
+        <v>0.00757646371516078</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>0.452767322977336</v>
@@ -1603,7 +1603,7 @@
         <v>56</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>-0.0470465837573028</v>
+        <v>0.0470465837573028</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>0.541756193160326</v>
@@ -1623,7 +1623,7 @@
         <v>57</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>-0.0663628167341162</v>
+        <v>0.0663628167341162</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>0.513803065772297</v>
@@ -1643,7 +1643,7 @@
         <v>58</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>0.0036830471097905</v>
+        <v>-0.0036830471097905</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>0.431433855358602</v>
@@ -1663,7 +1663,7 @@
         <v>59</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>-0.00457837798356689</v>
+        <v>0.00457837798356689</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>0.656015690463905</v>
@@ -1787,16 +1787,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>-0.250752966301378</v>
+        <v>0.250752966301378</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>0.0000000000000000208166817117217</v>
+        <v>-0.0000000000000000208166817117217</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.0000000000000000208166817117217</v>
+        <v>-0.0000000000000000208166817117217</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>-0.0000000000000000416333634234434</v>
+        <v>0.0000000000000000416333634234434</v>
       </c>
     </row>
     <row r="3">
@@ -1804,7 +1804,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>-0.250752966301378</v>
+        <v>0.250752966301378</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>1</v>
@@ -1824,7 +1824,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0.0000000000000000208166817117217</v>
+        <v>-0.0000000000000000208166817117217</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0000000000000000208166817117217</v>
+        <v>-0.0000000000000000208166817117217</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>-0.0000000000000000138777878078145</v>
@@ -1864,7 +1864,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>-0.0000000000000000416333634234434</v>
+        <v>0.0000000000000000416333634234434</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>-0.0000000000000000138777878078145</v>
